--- a/src/test/resources/test-data/CART_Data.xlsx
+++ b/src/test/resources/test-data/CART_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40b526981555a6cc/Project Workspace/Intellij Worksapce/E2EAutomation/src/test/resources/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_F25DC773A252ABDACC10489E89DB6DAE5BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12352A01-3123-4912-9232-A6BCA02960B7}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC10489E89DB6DAE5BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF1A7A7-193C-4967-A8E2-7A8C26BFD3FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>Availability</t>
   </si>
   <si>
-    <t>In Stock</t>
-  </si>
-  <si>
     <t>user can see correct product details for "ADIDAS ORIGINAL" in cart page after adding product to cart from homepage</t>
   </si>
   <si>
@@ -55,6 +52,9 @@
   </si>
   <si>
     <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>IN STOCK</t>
   </si>
 </sst>
 </file>
@@ -430,7 +430,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -472,13 +472,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
